--- a/artfynd/A 22333-2022 artfynd.xlsx
+++ b/artfynd/A 22333-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22333-2022 artfynd.xlsx
+++ b/artfynd/A 22333-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102889077</v>
+        <v>102889100</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Östbodarna, Jmt</t>
+          <t>Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467791.7904266735</v>
+        <v>467700</v>
       </c>
       <c r="R2" t="n">
-        <v>6932617.111769347</v>
+        <v>6932456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +748,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,60 +777,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102889048</v>
+        <v>102889108</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Östbodarna, Jmt</t>
+          <t>Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467730.3750873783</v>
+        <v>467700</v>
       </c>
       <c r="R3" t="n">
-        <v>6932626.481395999</v>
+        <v>6932456</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +846,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102889100</v>
+        <v>102889390</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,39 +886,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östbodarna, Jmt</t>
+          <t>N Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467699.5833532846</v>
+        <v>467694</v>
       </c>
       <c r="R4" t="n">
-        <v>6932455.913898092</v>
+        <v>6932695</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,19 +944,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,51 +973,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102889108</v>
+        <v>102889378</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östbodarna, Jmt</t>
+          <t>N Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467699.5833532846</v>
+        <v>467694</v>
       </c>
       <c r="R5" t="n">
-        <v>6932455.913898092</v>
+        <v>6932695</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,19 +1042,14 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vidsträckt förekomst under granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,51 +1076,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102889390</v>
+        <v>102888971</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Östbodarna, Jmt</t>
+          <t>N Östbodarna , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467693.5796607786</v>
+        <v>467647</v>
       </c>
       <c r="R6" t="n">
-        <v>6932694.721175899</v>
+        <v>6932653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,19 +1154,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102888971</v>
+        <v>102889012</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1213,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1308,14 +1224,14 @@
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Östbodarna , Jmt</t>
+          <t>N Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467647.39321325</v>
+        <v>467741</v>
       </c>
       <c r="R7" t="n">
-        <v>6932653.148093682</v>
+        <v>6932649</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,19 +1261,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,15 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102889012</v>
+        <v>102889030</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1320,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1434,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467741.2255653866</v>
+        <v>467725</v>
       </c>
       <c r="R8" t="n">
-        <v>6932648.541910032</v>
+        <v>6932595</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1467,19 +1368,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,51 +1397,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102889378</v>
+        <v>102889048</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>N Östbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467693.5796607786</v>
+        <v>467731</v>
       </c>
       <c r="R9" t="n">
-        <v>6932694.721175899</v>
+        <v>6932626</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1580,24 +1475,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vidsträckt förekomst under granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,15 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102889030</v>
+        <v>102889060</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467724.9837447207</v>
+        <v>467760</v>
       </c>
       <c r="R10" t="n">
-        <v>6932595.131895168</v>
+        <v>6932624</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1707,19 +1582,9 @@
           <t>2022-08-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,6 +1608,220 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102889069</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N Östbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467790</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6932585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102889077</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Östbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467792</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6932617</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22333-2022 artfynd.xlsx
+++ b/artfynd/A 22333-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889378</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102888971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889030</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889048</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889060</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889069</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,8 +1877,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102889077</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>